--- a/client/public/sample_campaign_tracker_import.xlsx
+++ b/client/public/sample_campaign_tracker_import.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="87">
   <si>
     <t>MEDIA BUZZ — CAMPAIGN TRACKER IMPORT TEMPLATE</t>
   </si>
@@ -23,12 +23,6 @@
     <t>Month</t>
   </si>
   <si>
-    <t>Occupancy</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>Client/Agency Name</t>
   </si>
   <si>
@@ -71,12 +65,6 @@
     <t>Total Amount</t>
   </si>
   <si>
-    <t>PO</t>
-  </si>
-  <si>
-    <t>Bill</t>
-  </si>
-  <si>
     <t>Pending</t>
   </si>
   <si>
@@ -86,75 +74,54 @@
     <t>Mar 2026</t>
   </si>
   <si>
-    <t>Occupied</t>
+    <t>Tata Motors Passenger Vehicles</t>
+  </si>
+  <si>
+    <t>Tata Curvv EV Campaign</t>
+  </si>
+  <si>
+    <t>Media Buzz</t>
+  </si>
+  <si>
+    <t>Shivranjani Bridge- Nr.D Mart Junction - Left (1)</t>
+  </si>
+  <si>
+    <t>30x10 ft</t>
+  </si>
+  <si>
+    <t>Hoarding</t>
   </si>
   <si>
     <t>2026-03-01</t>
   </si>
   <si>
-    <t>Tata Motors Passenger Vehicles</t>
-  </si>
-  <si>
-    <t>Tata Curvv EV Campaign</t>
-  </si>
-  <si>
-    <t>Media Buzz</t>
-  </si>
-  <si>
-    <t>Shivranjani Bridge- Nr.D Mart Junction - Left (1)</t>
-  </si>
-  <si>
-    <t>30x10 ft</t>
-  </si>
-  <si>
-    <t>Hoarding</t>
-  </si>
-  <si>
     <t>2026-03-31</t>
   </si>
   <si>
-    <t>PO-TAT-2026-001</t>
-  </si>
-  <si>
-    <t>INV-MB-2026-101</t>
-  </si>
-  <si>
     <t>MB-02</t>
   </si>
   <si>
+    <t>HDFC Bank Ltd</t>
+  </si>
+  <si>
+    <t>Festive Home Loan 8.40%</t>
+  </si>
+  <si>
+    <t>Shivranjani Bridge- Nr.D Mart Junction - Middel (2)</t>
+  </si>
+  <si>
     <t>2026-03-05</t>
   </si>
   <si>
-    <t>HDFC Bank Ltd</t>
-  </si>
-  <si>
-    <t>Festive Home Loan 8.40%</t>
-  </si>
-  <si>
-    <t>Shivranjani Bridge- Nr.D Mart Junction - Middel (2)</t>
-  </si>
-  <si>
     <t>2026-04-04</t>
   </si>
   <si>
-    <t>HDFC-OOH-2026-44</t>
-  </si>
-  <si>
-    <t>INV-MB-2026-102</t>
-  </si>
-  <si>
     <t>MB-03</t>
   </si>
   <si>
     <t>Apr 2026</t>
   </si>
   <si>
-    <t>Upcoming</t>
-  </si>
-  <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
     <t>Samsung India Electronics</t>
   </si>
   <si>
@@ -170,45 +137,30 @@
     <t>2026-04-30</t>
   </si>
   <si>
-    <t>SAMS-ADV-9921</t>
+    <t>MB-04</t>
+  </si>
+  <si>
+    <t>Adani Wilmar Limited</t>
+  </si>
+  <si>
+    <t>Fortune Sunflower Oil Brand Awareness</t>
+  </si>
+  <si>
+    <t>Shivranjani Bridge- Nr.D Mart Junction (1-3)</t>
+  </si>
+  <si>
+    <t>92.5x10 ft</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>MB-05</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>MB-04</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>Adani Wilmar Limited</t>
-  </si>
-  <si>
-    <t>Fortune Sunflower Oil Brand Awareness</t>
-  </si>
-  <si>
-    <t>Shivranjani Bridge- Nr.D Mart Junction (1-3)</t>
-  </si>
-  <si>
-    <t>92.5x10 ft</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>AWL-RO-8871</t>
-  </si>
-  <si>
-    <t>INV-MB-2026-095</t>
-  </si>
-  <si>
-    <t>MB-05</t>
-  </si>
-  <si>
-    <t>Vacant</t>
-  </si>
-  <si>
     <t>Shivranjani Bridge- Nr.D Mart Junction - Middel - Left (2-1)</t>
   </si>
   <si>
@@ -245,54 +197,45 @@
     <t>Billing period or campaign month.</t>
   </si>
   <si>
-    <t>Occupied / Vacant / Upcoming</t>
-  </si>
-  <si>
-    <t>Visual status tag. Sites with active dates automatically show Occupied.</t>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>Tata Motors Ltd</t>
+  </si>
+  <si>
+    <t>Client or booking agency name.</t>
+  </si>
+  <si>
+    <t>Campaign creative, brand, or display text.</t>
+  </si>
+  <si>
+    <t>Media owner, partner, or supplier name.</t>
+  </si>
+  <si>
+    <t>Shivranjani Bridge- Nr.D Mart</t>
+  </si>
+  <si>
+    <t>Site location / address. Used for auto-matching if site code is missing.</t>
+  </si>
+  <si>
+    <t>W &amp; H</t>
+  </si>
+  <si>
+    <t>30 &amp; 10</t>
+  </si>
+  <si>
+    <t>Width and height in feet.</t>
+  </si>
+  <si>
+    <t>Dimensions string (e.g. 30x10 or 30x10 ft).</t>
+  </si>
+  <si>
+    <t>Media type (Hoarding, Unipole, Gantry, etc.). Default: Hoarding.</t>
   </si>
   <si>
     <t>2026-03-01 or 01/03/2026</t>
   </si>
   <si>
-    <t>Booking or agreement date.</t>
-  </si>
-  <si>
-    <t>Important</t>
-  </si>
-  <si>
-    <t>Tata Motors Ltd</t>
-  </si>
-  <si>
-    <t>Client or booking agency name.</t>
-  </si>
-  <si>
-    <t>Campaign creative, brand, or display text.</t>
-  </si>
-  <si>
-    <t>Media owner, partner, or supplier name.</t>
-  </si>
-  <si>
-    <t>Shivranjani Bridge- Nr.D Mart</t>
-  </si>
-  <si>
-    <t>Site location / address. Used for auto-matching if site code is missing.</t>
-  </si>
-  <si>
-    <t>W &amp; H</t>
-  </si>
-  <si>
-    <t>30 &amp; 10</t>
-  </si>
-  <si>
-    <t>Width and height in feet.</t>
-  </si>
-  <si>
-    <t>Dimensions string (e.g. 30x10 or 30x10 ft).</t>
-  </si>
-  <si>
-    <t>Media type (Hoarding, Unipole, Gantry, etc.). Default: Hoarding.</t>
-  </si>
-  <si>
     <t>Campaign live start date. Formats: YYYY-MM-DD, DD/MM/YYYY, DD-MM-YYYY, DD-MMM-YYYY.</t>
   </si>
   <si>
@@ -324,12 +267,6 @@
   </si>
   <si>
     <t>Total gross amount (₹). Auto-sums Advt Fees + Printing/Mounting if blank.</t>
-  </si>
-  <si>
-    <t>Purchase Order / Release Order (RO) number.</t>
-  </si>
-  <si>
-    <t>Invoice / Bill number.</t>
   </si>
   <si>
     <t>0 or 50000</t>
@@ -345,7 +282,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="₹#,##0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -371,29 +308,17 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF2563EB"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF16A34A"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
@@ -473,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -490,9 +415,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -502,41 +424,35 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -878,29 +794,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="16" max="17" width="22" customWidth="1"/>
-    <col min="18" max="18" width="20" customWidth="1"/>
-    <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="20" customWidth="1"/>
-    <col min="21" max="21" width="18" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" ht="40" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -920,22 +833,18 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -944,10 +853,10 @@
       <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -965,10 +874,10 @@
       <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="4" t="s">
         <v>15</v>
       </c>
       <c r="P2" s="4" t="s">
@@ -977,347 +886,275 @@
       <c r="Q2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="4" t="s">
+    </row>
+    <row r="3" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" ht="23" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="G3" s="5">
+        <v>30</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="K3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="L3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="M3" s="5">
+        <v>31</v>
+      </c>
+      <c r="N3" s="7">
+        <v>250000</v>
+      </c>
+      <c r="O3" s="7">
+        <v>20000</v>
+      </c>
+      <c r="P3" s="7">
+        <v>270000</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="5">
+      <c r="D4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="5">
+      <c r="E4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="8">
+        <v>30</v>
+      </c>
+      <c r="H4" s="8">
         <v>10</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="I4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="8">
+        <v>31</v>
+      </c>
+      <c r="N4" s="10">
+        <v>240000</v>
+      </c>
+      <c r="O4" s="10">
+        <v>18000</v>
+      </c>
+      <c r="P4" s="10">
+        <v>258000</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="5" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="5">
         <v>30</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="5" t="s">
+      <c r="H5" s="5">
+        <v>10</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="5">
-        <v>31</v>
-      </c>
-      <c r="P3" s="8">
-        <v>250000</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>20000</v>
-      </c>
-      <c r="R3" s="8">
-        <v>270000</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U3" s="8">
+      <c r="K5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="5">
+        <v>30</v>
+      </c>
+      <c r="N5" s="7">
+        <v>260000</v>
+      </c>
+      <c r="O5" s="7">
+        <v>22000</v>
+      </c>
+      <c r="P5" s="7">
+        <v>282000</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>282000</v>
+      </c>
+    </row>
+    <row r="6" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="8">
+        <v>92.5</v>
+      </c>
+      <c r="H6" s="8">
+        <v>10</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="8">
+        <v>92</v>
+      </c>
+      <c r="N6" s="10">
+        <v>650000</v>
+      </c>
+      <c r="O6" s="10">
+        <v>55000</v>
+      </c>
+      <c r="P6" s="10">
+        <v>705000</v>
+      </c>
+      <c r="Q6" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="23" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="9">
-        <v>30</v>
-      </c>
-      <c r="J4" s="9">
+    <row r="7" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="5">
+        <v>61</v>
+      </c>
+      <c r="H7" s="5">
         <v>10</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="O4" s="9">
-        <v>31</v>
-      </c>
-      <c r="P4" s="12">
-        <v>240000</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>18000</v>
-      </c>
-      <c r="R4" s="12">
-        <v>258000</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="T4" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="U4" s="12">
-        <v>58000</v>
-      </c>
-    </row>
-    <row r="5" ht="23" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="I7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="5">
-        <v>30</v>
-      </c>
-      <c r="J5" s="5">
-        <v>10</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" s="5">
-        <v>30</v>
-      </c>
-      <c r="P5" s="8">
-        <v>260000</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>22000</v>
-      </c>
-      <c r="R5" s="8">
-        <v>282000</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="U5" s="8">
-        <v>282000</v>
-      </c>
-    </row>
-    <row r="6" ht="23" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" s="9">
-        <v>92.5</v>
-      </c>
-      <c r="J6" s="9">
-        <v>10</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="O6" s="9">
-        <v>92</v>
-      </c>
-      <c r="P6" s="12">
-        <v>650000</v>
-      </c>
-      <c r="Q6" s="12">
-        <v>55000</v>
-      </c>
-      <c r="R6" s="12">
-        <v>705000</v>
-      </c>
-      <c r="S6" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="T6" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="U6" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="23" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" s="5">
-        <v>61</v>
-      </c>
-      <c r="J7" s="5">
-        <v>10</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>66</v>
-      </c>
       <c r="L7" s="5" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="P7" s="8">
+        <v>48</v>
+      </c>
+      <c r="N7" s="7">
         <v>400000</v>
       </c>
-      <c r="Q7" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="R7" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="U7" s="15" t="s">
-        <v>53</v>
+      <c r="O7" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1326,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1336,305 +1173,249 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B9" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="D9" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="17" t="s">
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="13" t="s">
+    <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="18" t="s">
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D12" s="16" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="20" t="s">
+    <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="19" t="s">
+      <c r="D13" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="18" t="s">
+    <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="19" t="s">
+    <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D15" s="14" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="13" t="s">
+    <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="D16" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="18" t="s">
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="19" t="s">
+      <c r="D17" s="14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="18" t="s">
+    <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="19" t="s">
+      <c r="D18" s="16" t="s">
         <v>86</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/sample_campaign_tracker_import.xlsx
+++ b/client/public/sample_campaign_tracker_import.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Campaign Tracker" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Latest Booking" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Instructions &amp; Guide" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="87">
   <si>
-    <t>MEDIA BUZZ — CAMPAIGN TRACKER IMPORT TEMPLATE</t>
+    <t>MEDIA BUZZ — LATEST BOOKING IMPORT TEMPLATE</t>
   </si>
   <si>
     <t>Site Code</t>
@@ -167,7 +167,7 @@
     <t>61x10 ft</t>
   </si>
   <si>
-    <t>CAMPAIGN TRACKER IMPORT FIELD SPECIFICATION GUIDE</t>
+    <t>LATEST BOOKING IMPORT FIELD SPECIFICATION GUIDE</t>
   </si>
   <si>
     <t>Column Header</t>
